--- a/out/LSTM-Mamba1_repeat_results.xlsx
+++ b/out/LSTM-Mamba1_repeat_results.xlsx
@@ -476,10 +476,10 @@
         <v>0.5154666666666667</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03328302502632141</v>
+        <v>0.03328302130103111</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.005291640758514404</v>
+        <v>-0.005291712284088135</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         <v>0.5154666666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03328302502632141</v>
+        <v>0.03328302130103111</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.005291640758514404</v>
+        <v>-0.005291712284088135</v>
       </c>
     </row>
     <row r="4">
@@ -520,10 +520,10 @@
         <v>0.5154666666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03328302502632141</v>
+        <v>0.03328302130103111</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.005291640758514404</v>
+        <v>-0.005291712284088135</v>
       </c>
     </row>
     <row r="5">
@@ -542,10 +542,10 @@
         <v>0.5154666666666667</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03328302502632141</v>
+        <v>0.03328302130103111</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.005291640758514404</v>
+        <v>-0.005291712284088135</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>0.5154666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03328302502632141</v>
+        <v>0.03328302130103111</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.005291640758514404</v>
+        <v>-0.005291712284088135</v>
       </c>
     </row>
     <row r="7">
@@ -586,10 +586,10 @@
         <v>0.5154666666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03328302502632141</v>
+        <v>0.03328302130103111</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.005291640758514404</v>
+        <v>-0.005291712284088135</v>
       </c>
     </row>
   </sheetData>
